--- a/output/pdf_financials_xlsx/WTE.xlsx
+++ b/output/pdf_financials_xlsx/WTE.xlsx
@@ -6038,7 +6038,7 @@
         <v>-45.01</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>42.993</v>
+        <v>-42.993</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>64.657</v>
@@ -27156,7 +27156,7 @@
         <v>-45.01</v>
       </c>
       <c r="G208" s="5" t="n">
-        <v>42.993</v>
+        <v>-42.993</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>-45.01</v>
       </c>
       <c r="G304" s="5" t="n">
-        <v>42.993</v>
+        <v>-42.993</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WTE.xlsx
+++ b/output/pdf_financials_xlsx/WTE.xlsx
@@ -999,16 +999,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.373</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.196</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1902,16 +1902,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>107.118</v>
+        <v>106.745</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>83.498</v>
+        <v>83.066</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>58.924</v>
+        <v>58.79</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>86.005</v>
+        <v>85.809</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>179.912</v>
@@ -2012,16 +2012,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>128.497</v>
+        <v>128.124</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>105.43</v>
+        <v>104.998</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>68.96599999999999</v>
+        <v>68.83199999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>95.875</v>
+        <v>95.679</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>191.44</v>
@@ -2067,16 +2067,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>61.84340979314461</v>
+        <v>61.66389126856549</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>47.16466251521008</v>
+        <v>46.97140505332474</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>32.40320057132923</v>
+        <v>32.34024159333199</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>39.83256818795572</v>
+        <v>39.7511373314776</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>64.73581875052837</v>
@@ -34572,7 +34572,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -34670,7 +34670,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -36574,7 +36574,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E311" s="5" t="n">

--- a/output/pdf_financials_xlsx/WTE.xlsx
+++ b/output/pdf_financials_xlsx/WTE.xlsx
@@ -1057,49 +1057,49 @@
         <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>131.362</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>38.847</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-21.967</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-3.569</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>2.972</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>3.671</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>3.707</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>2.793</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>11.84</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>11.4</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>10.658</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>8.673</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>4.302</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>17.333</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0</v>
+        <v>19.747</v>
       </c>
     </row>
     <row r="14">
@@ -1905,49 +1905,49 @@
         <v>106.745</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>83.066</v>
+        <v>-48.296</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>58.79</v>
+        <v>19.943</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>85.809</v>
+        <v>107.776</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>179.912</v>
+        <v>183.481</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>176.577</v>
+        <v>173.605</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>206.692</v>
+        <v>203.021</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>161.453</v>
+        <v>157.746</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>148.916</v>
+        <v>146.123</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>169.883</v>
+        <v>158.043</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>190.998</v>
+        <v>179.598</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>147.663</v>
+        <v>137.005</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>91.657</v>
+        <v>82.98399999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>159.73</v>
+        <v>155.428</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>157.967</v>
+        <v>140.634</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>124.323</v>
+        <v>104.576</v>
       </c>
     </row>
     <row r="28">
@@ -2015,49 +2015,49 @@
         <v>128.124</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>104.998</v>
+        <v>-26.364</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>68.83199999999999</v>
+        <v>29.985</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>95.679</v>
+        <v>117.646</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>191.44</v>
+        <v>195.009</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>187.126</v>
+        <v>184.154</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>217.155</v>
+        <v>213.484</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>174.833</v>
+        <v>171.126</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>165.95</v>
+        <v>163.157</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>192.573</v>
+        <v>180.733</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>215.866</v>
+        <v>204.466</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>176.082</v>
+        <v>165.424</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>121.88</v>
+        <v>113.207</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>190.259</v>
+        <v>185.957</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>191.935</v>
+        <v>174.602</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>157.499</v>
+        <v>137.752</v>
       </c>
     </row>
     <row r="30">
@@ -2070,49 +2070,49 @@
         <v>61.66389126856549</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>46.97140505332474</v>
+        <v>-11.79407343783552</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>32.34024159333199</v>
+        <v>14.08824593468241</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>39.7511373314776</v>
+        <v>48.87762521032842</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>64.73581875052837</v>
+        <v>65.94268323611463</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>59.96186814067131</v>
+        <v>59.00953296483217</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>59.36164803713332</v>
+        <v>58.3581408190434</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>53.88380185105852</v>
+        <v>52.74129869969766</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>50.28315521875217</v>
+        <v>49.43687108180747</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>52.9965407065545</v>
+        <v>49.73814497108999</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>54.59129739872844</v>
+        <v>51.708301510791</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>51.71718002414303</v>
+        <v>48.58681062410602</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>41.04297928656337</v>
+        <v>38.12235441494897</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>49.93740075329073</v>
+        <v>48.80825207679891</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>47.42309051241695</v>
+        <v>43.14047177246997</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>48.76069646196332</v>
+        <v>42.64714988049684</v>
       </c>
     </row>
     <row r="31">
@@ -30182,7 +30182,11 @@
           <t>Net finance costs 7</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -31574,7 +31578,11 @@
           <t>Net finance costs 7</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -32052,7 +32060,11 @@
           <t>Net finance costs 7</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -32488,7 +32500,11 @@
           <t>Net finance costs 6</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -34766,7 +34782,11 @@
           <t>Net finance costs 5</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WTE.xlsx
+++ b/output/pdf_financials_xlsx/WTE.xlsx
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.012</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0.307</v>
@@ -1502,10 +1502,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>107.106</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-45.01</v>
@@ -1670,7 +1668,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>107.118</v>
+        <v>107.106</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-45.01</v>
@@ -2122,7 +2120,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>0.01120259900296869</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>0.367673477209035</v>
@@ -2177,7 +2175,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>51.55406250902406</v>
+        <v>51.54828711413143</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>-20.13545916541407</v>
@@ -6032,7 +6030,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>107.118</v>
+        <v>107.106</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-45.01</v>
@@ -7292,31 +7290,31 @@
         <v>0</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-10.321</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-5.781</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-60.856</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-88.514</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-17.228</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-2.076</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-10.086</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-7.582</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-17.656</v>
       </c>
       <c r="Q121" s="3" t="n">
         <v>0</v>
@@ -23296,7 +23294,11 @@
           <t>Share purchases</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -25144,7 +25146,11 @@
           <t>Share repurchases</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -28098,7 +28104,11 @@
           <t>Future income tax recovery (note 6)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E218" s="5" t="n">
         <v>-0.012</v>
       </c>
@@ -36886,7 +36896,11 @@
           <t>Future income tax recovery (note 6)</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E314" s="5" t="n">
         <v>0.012</v>
       </c>
